--- a/diseases/d208/1995-1999.xlsx
+++ b/diseases/d208/1995-1999.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28698,7 +28698,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32598,7 +32598,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33378,7 +33378,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34158,7 +34158,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35718,7 +35718,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36498,7 +36498,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37278,7 +37278,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38058,7 +38058,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39618,7 +39618,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41178,7 +41178,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41958,7 +41958,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42738,7 +42738,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43518,7 +43518,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44298,7 +44298,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46638,7 +46638,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47418,7 +47418,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">

--- a/diseases/d208/1995-1999.xlsx
+++ b/diseases/d208/1995-1999.xlsx
@@ -1398,7 +1398,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25578,7 +25578,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -27138,7 +27138,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27918,7 +27918,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28698,7 +28698,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31038,7 +31038,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31818,7 +31818,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32598,7 +32598,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33378,7 +33378,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34158,7 +34158,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35718,7 +35718,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36498,7 +36498,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37278,7 +37278,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38058,7 +38058,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39618,7 +39618,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40398,7 +40398,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41178,7 +41178,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41958,7 +41958,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42738,7 +42738,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43518,7 +43518,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44298,7 +44298,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45858,7 +45858,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46638,7 +46638,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47418,7 +47418,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN241" t="b">
